--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.55486069219882</v>
+        <v>9.515164862482308</v>
       </c>
       <c r="D2" t="n">
-        <v>57.92274319018757</v>
+        <v>9.41244576840548</v>
       </c>
       <c r="E2" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F2" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>80.15003795926846</v>
+        <v>13.02438116838113</v>
       </c>
       <c r="D3" t="n">
-        <v>79.75089739481108</v>
+        <v>12.9595208266568</v>
       </c>
       <c r="E3" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F3" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.7924905207727</v>
+        <v>8.253779709625563</v>
       </c>
       <c r="D4" t="n">
-        <v>50.14233596568647</v>
+        <v>8.148129594424052</v>
       </c>
       <c r="E4" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F4" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.27329947804945</v>
+        <v>8.819411165183036</v>
       </c>
       <c r="D5" t="n">
-        <v>53.67418426297049</v>
+        <v>8.722054942732706</v>
       </c>
       <c r="E5" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F5" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.36850503004973</v>
+        <v>6.55988206738308</v>
       </c>
       <c r="D6" t="n">
-        <v>39.71964268542953</v>
+        <v>6.4544419363823</v>
       </c>
       <c r="E6" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F6" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>61.89483926003219</v>
+        <v>10.05791137975523</v>
       </c>
       <c r="D7" t="n">
-        <v>61.51319861997668</v>
+        <v>9.995894775746212</v>
       </c>
       <c r="E7" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F7" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.00144013904166</v>
+        <v>6.82523402259427</v>
       </c>
       <c r="D8" t="n">
-        <v>41.46174517350672</v>
+        <v>6.737533590694842</v>
       </c>
       <c r="E8" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F8" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.76746206154919</v>
+        <v>5.162212585001743</v>
       </c>
       <c r="D9" t="n">
-        <v>31.12573648380805</v>
+        <v>5.057932178618809</v>
       </c>
       <c r="E9" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F9" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.47677125896929</v>
+        <v>5.439975329582509</v>
       </c>
       <c r="D10" t="n">
-        <v>32.94267229769451</v>
+        <v>5.353184248375359</v>
       </c>
       <c r="E10" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F10" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.59057547443004</v>
+        <v>6.920968514594882</v>
       </c>
       <c r="D11" t="n">
-        <v>42.15525656830534</v>
+        <v>6.850229192349618</v>
       </c>
       <c r="E11" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F11" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.56143310778105</v>
+        <v>6.428732880014421</v>
       </c>
       <c r="D12" t="n">
-        <v>39.18846073257001</v>
+        <v>6.368124869042626</v>
       </c>
       <c r="E12" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F12" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50.82159596077812</v>
+        <v>8.258509343626445</v>
       </c>
       <c r="D13" t="n">
-        <v>50.55390620116298</v>
+        <v>8.215009757688986</v>
       </c>
       <c r="E13" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F13" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.09765965401774</v>
+        <v>4.890869693777883</v>
       </c>
       <c r="D14" t="n">
-        <v>29.66028798371312</v>
+        <v>4.819796797353383</v>
       </c>
       <c r="E14" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F14" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.95040591868863</v>
+        <v>3.079440961786902</v>
       </c>
       <c r="D15" t="n">
-        <v>18.58999787042816</v>
+        <v>3.020874653944575</v>
       </c>
       <c r="E15" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F15" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42843497566672</v>
+        <v>3.157120683545843</v>
       </c>
       <c r="D16" t="n">
-        <v>19.23914295526504</v>
+        <v>3.126360730230569</v>
       </c>
       <c r="E16" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F16" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.20632437265596</v>
+        <v>5.071027710556594</v>
       </c>
       <c r="D17" t="n">
-        <v>31.18377125375428</v>
+        <v>5.067362828735071</v>
       </c>
       <c r="E17" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F17" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.66391144837823</v>
+        <v>3.357885610361463</v>
       </c>
       <c r="D18" t="n">
-        <v>21.29260426853238</v>
+        <v>3.460048193636512</v>
       </c>
       <c r="E18" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F18" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.23692080644093</v>
+        <v>6.213499631046652</v>
       </c>
       <c r="D19" t="n">
-        <v>38.77749341783025</v>
+        <v>6.301342680397416</v>
       </c>
       <c r="E19" t="n">
-        <v>15.59693371475781</v>
+        <v>2.534501728648145</v>
       </c>
       <c r="F19" t="n">
-        <v>15.46888362142125</v>
+        <v>2.513693588480954</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
